--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4947" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4947" uniqueCount="456">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -808,6 +808,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Observation.statusCode</t>
   </si>
   <si>
@@ -850,8 +854,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Observation.interpretationCode</t>
@@ -7091,7 +7095,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>258</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -7099,10 +7103,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7158,25 +7162,25 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7196,10 +7200,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7222,13 +7226,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7279,7 +7283,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7299,10 +7303,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7325,7 +7329,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7358,7 +7362,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7376,7 +7380,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7396,10 +7400,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7422,7 +7426,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7475,7 +7479,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7495,10 +7499,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7554,25 +7558,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7592,10 +7596,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7618,7 +7622,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7671,7 +7675,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7691,10 +7695,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7717,7 +7721,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7750,25 +7754,25 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7788,10 +7792,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7814,7 +7818,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7847,25 +7851,25 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7885,10 +7889,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7915,7 +7919,7 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7966,7 +7970,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7986,10 +7990,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8012,7 +8016,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -8065,7 +8069,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8085,10 +8089,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8111,7 +8115,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -8164,7 +8168,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8184,10 +8188,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8210,7 +8214,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8263,7 +8267,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8283,10 +8287,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8309,7 +8313,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8362,7 +8366,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8382,10 +8386,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8408,7 +8412,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8461,7 +8465,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8481,10 +8485,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8507,7 +8511,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8560,7 +8564,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8580,10 +8584,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8606,7 +8610,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8647,7 +8651,7 @@
         <v>74</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
@@ -8657,7 +8661,7 @@
         <v>124</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8677,13 +8681,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -8705,10 +8709,10 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -8760,7 +8764,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8780,10 +8784,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8881,10 +8885,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8982,10 +8986,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9083,10 +9087,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9184,10 +9188,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9287,10 +9291,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9390,10 +9394,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9493,10 +9497,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9596,10 +9600,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9697,10 +9701,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9737,7 +9741,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -9756,7 +9760,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9774,7 +9778,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -9794,10 +9798,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9824,7 +9828,7 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9875,7 +9879,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9895,10 +9899,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9925,12 +9929,12 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
@@ -9976,7 +9980,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9996,10 +10000,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10075,7 +10079,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10095,10 +10099,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10121,7 +10125,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10174,7 +10178,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10194,10 +10198,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10220,7 +10224,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10273,7 +10277,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10293,10 +10297,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10319,7 +10323,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10372,7 +10376,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10392,10 +10396,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10418,7 +10422,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10471,7 +10475,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10491,10 +10495,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10517,7 +10521,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10570,7 +10574,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10590,10 +10594,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10616,7 +10620,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10669,7 +10673,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10689,10 +10693,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10715,7 +10719,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10768,7 +10772,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10788,10 +10792,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10814,7 +10818,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10867,7 +10871,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10887,10 +10891,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10913,7 +10917,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10966,7 +10970,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10986,10 +10990,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11012,7 +11016,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -11065,7 +11069,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11085,10 +11089,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11111,7 +11115,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11164,7 +11168,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11184,13 +11188,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>74</v>
@@ -11212,10 +11216,10 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -11267,7 +11271,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11287,10 +11291,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11388,10 +11392,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11489,10 +11493,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11590,10 +11594,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11691,10 +11695,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11794,10 +11798,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11897,10 +11901,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12000,10 +12004,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12103,10 +12107,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12204,10 +12208,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12263,7 +12267,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>74</v>
@@ -12281,7 +12285,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -12301,10 +12305,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12331,7 +12335,7 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12382,7 +12386,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12402,10 +12406,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12432,12 +12436,12 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12483,7 +12487,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12503,10 +12507,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12582,7 +12586,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12602,10 +12606,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12628,7 +12632,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12681,7 +12685,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12701,10 +12705,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12727,7 +12731,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12780,7 +12784,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12800,10 +12804,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12826,7 +12830,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12879,7 +12883,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12899,10 +12903,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12925,7 +12929,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12978,7 +12982,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12998,10 +13002,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13024,7 +13028,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13077,7 +13081,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13097,10 +13101,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13123,7 +13127,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13176,7 +13180,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13196,10 +13200,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13222,7 +13226,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13275,7 +13279,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13295,10 +13299,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13321,7 +13325,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13374,7 +13378,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13394,10 +13398,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13420,7 +13424,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13473,7 +13477,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13493,10 +13497,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13519,7 +13523,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13572,7 +13576,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13592,10 +13596,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13618,7 +13622,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13671,7 +13675,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13691,13 +13695,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>74</v>
@@ -13719,10 +13723,10 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -13774,7 +13778,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13794,10 +13798,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13895,10 +13899,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13996,10 +14000,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14097,10 +14101,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14198,10 +14202,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14301,10 +14305,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14404,10 +14408,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14507,10 +14511,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14610,10 +14614,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14711,10 +14715,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14751,7 +14755,7 @@
         <v>74</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>74</v>
@@ -14770,7 +14774,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>74</v>
@@ -14788,7 +14792,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -14808,10 +14812,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14838,7 +14842,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14889,7 +14893,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14909,10 +14913,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14939,12 +14943,12 @@
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
@@ -14990,7 +14994,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15010,10 +15014,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15089,7 +15093,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15109,10 +15113,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15135,7 +15139,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15188,7 +15192,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15208,10 +15212,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15234,7 +15238,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15287,7 +15291,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15307,10 +15311,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15333,7 +15337,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15386,7 +15390,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15406,10 +15410,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15432,7 +15436,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15485,7 +15489,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15505,10 +15509,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15531,7 +15535,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15584,7 +15588,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15604,10 +15608,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15630,7 +15634,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15683,7 +15687,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15703,10 +15707,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15729,7 +15733,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15782,7 +15786,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15802,10 +15806,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15828,7 +15832,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -15881,7 +15885,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15901,10 +15905,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15927,7 +15931,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -15980,7 +15984,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16000,10 +16004,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16026,7 +16030,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16079,7 +16083,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16099,10 +16103,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16125,7 +16129,7 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16178,7 +16182,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16198,10 +16202,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16224,7 +16228,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16277,7 +16281,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16297,10 +16301,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16323,7 +16327,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16376,7 +16380,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16396,10 +16400,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16422,7 +16426,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16475,7 +16479,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16495,10 +16499,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16521,11 +16525,11 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -16576,7 +16580,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16596,10 +16600,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16697,10 +16701,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16798,10 +16802,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16899,10 +16903,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17000,10 +17004,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17103,10 +17107,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17206,10 +17210,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17309,10 +17313,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17412,10 +17416,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17513,10 +17517,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17550,7 +17554,7 @@
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>74</v>
@@ -17572,7 +17576,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>74</v>
@@ -17590,7 +17594,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17610,10 +17614,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17636,7 +17640,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17689,7 +17693,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>75</v>
@@ -17709,10 +17713,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17735,7 +17739,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17788,7 +17792,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
